--- a/data/trans_orig/IP04D$aparatos-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24531</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37604</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>57481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76478</t>
+          <t>75847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>40769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63365</t>
+          <t>63786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64539</t>
+          <t>64202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80162</t>
+          <t>79816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80045</t>
+          <t>79731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132640</t>
+          <t>132580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155145</t>
+          <t>154892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>39866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58800</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81305</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56857</t>
+          <t>56164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61131</t>
+          <t>60889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97055</t>
+          <t>97415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23529</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51443</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57620</t>
+          <t>57811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82829</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105272</t>
+          <t>104152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24614</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>39657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77166</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>21591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>45655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>61350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28636</t>
+          <t>29303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44234</t>
+          <t>44998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30850</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>40215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73834</t>
+          <t>74224</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>41312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>95605</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113369</t>
+          <t>112574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99629</t>
+          <t>99058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117521</t>
+          <t>116588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200094</t>
+          <t>201156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224689</t>
+          <t>226102</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42670</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84363</t>
+          <t>83301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72098</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92304</t>
+          <t>93519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65362</t>
+          <t>64877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86246</t>
+          <t>85161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143845</t>
+          <t>144040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171659</t>
+          <t>173422</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>92734</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85069</t>
+          <t>86154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105953</t>
+          <t>106438</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>163574</t>
+          <t>161811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191388</t>
+          <t>191193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>435016</t>
+          <t>433746</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>476483</t>
+          <t>477138</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>442269</t>
+          <t>444078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>486898</t>
+          <t>487362</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>890540</t>
+          <t>890450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>951405</t>
+          <t>953410</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>273276</t>
+          <t>274546</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>265327</t>
+          <t>264863</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309956</t>
+          <t>308147</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>509112</t>
+          <t>507107</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>569977</t>
+          <t>570067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45726</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49059</t>
+          <t>49212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98154</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110849</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48865</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>44357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65929</t>
+          <t>65530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89910</t>
+          <t>89299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55082</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65446</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82227</t>
+          <t>81439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124320</t>
+          <t>124931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148301</t>
+          <t>148700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44707</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>96918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113197</t>
+          <t>112996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41166</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>41783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84255</t>
+          <t>85961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105508</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24579</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>39401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51802</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>71349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44055</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71585</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82026</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>39192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81631</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96540</t>
+          <t>95496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>57665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>76204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63412</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83416</t>
+          <t>82781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>127182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154036</t>
+          <t>157095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60193</t>
+          <t>60398</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78860</t>
+          <t>78937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56494</t>
+          <t>57129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76498</t>
+          <t>77060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122476</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149907</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93764</t>
+          <t>93858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113419</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101447</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>201310</t>
+          <t>199902</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229043</t>
+          <t>229583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50757</t>
+          <t>51146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70412</t>
+          <t>70318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68731</t>
+          <t>67977</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133044</t>
+          <t>134452</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>341465</t>
+          <t>340584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>382945</t>
+          <t>383439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>366690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>413510</t>
+          <t>411755</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>720906</t>
+          <t>722137</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>781491</t>
+          <t>784270</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>317236</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>358716</t>
+          <t>359597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>326501</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>372413</t>
+          <t>373321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>658701</t>
+          <t>655922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>719286</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36258</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>56822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>46215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61127</t>
+          <t>61418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>95826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116390</t>
+          <t>116286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108637</t>
+          <t>108547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122638</t>
+          <t>122862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102349</t>
+          <t>101680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116554</t>
+          <t>116852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>213856</t>
+          <t>215770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236548</t>
+          <t>237562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>48275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>70752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88252</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53710</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33116</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>62732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82326</t>
+          <t>81842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109158</t>
+          <t>109475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71930</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29036</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51495</t>
+          <t>51875</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27150</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50858</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66443</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84549</t>
+          <t>84916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76154</t>
+          <t>76603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95454</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112975</t>
+          <t>112085</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133234</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195028</t>
+          <t>194661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>224717</t>
+          <t>223947</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117180</t>
+          <t>116829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126549</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140253</t>
+          <t>140874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151031</t>
+          <t>151038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262430</t>
+          <t>260726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275640</t>
+          <t>275294</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>390190</t>
+          <t>391941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>449372</t>
+          <t>454634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>413919</t>
+          <t>411370</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>476641</t>
+          <t>473302</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>820184</t>
+          <t>822563</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>907555</t>
+          <t>903394</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>215784</t>
+          <t>210522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>274966</t>
+          <t>273215</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>283681</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>346403</t>
+          <t>348952</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>517922</t>
+          <t>522083</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>605293</t>
+          <t>602914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
